--- a/sources/jack2_step2.xlsx
+++ b/sources/jack2_step2.xlsx
@@ -2814,9 +2814,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <f>~3+4</f>
-        <v/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2841,6 +2842,11 @@
       <c r="G83" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2863,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2880,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2917,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5633,9 +5639,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>~3+4</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5660,6 +5667,11 @@
       <c r="J87" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5703,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5735,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5767,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
